--- a/Management/My Stats.xlsx
+++ b/Management/My Stats.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9654FA1F-A846-4902-96A3-C4ED5BCDC9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA8D097-87E7-4796-9FFA-2CCCECB94272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{5657D6CA-B9A7-4F85-9D0E-7B791CB3A74D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{5657D6CA-B9A7-4F85-9D0E-7B791CB3A74D}"/>
   </bookViews>
   <sheets>
     <sheet name="Macronutrients" sheetId="1" r:id="rId1"/>
     <sheet name="Meal Plan" sheetId="2" r:id="rId2"/>
     <sheet name="Measures Tracker" sheetId="3" r:id="rId3"/>
+    <sheet name="Supplements History" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="85">
   <si>
     <t>Total Weight [kg]</t>
   </si>
@@ -238,14 +239,75 @@
   </si>
   <si>
     <t>Whey Protein</t>
+  </si>
+  <si>
+    <t>Supplement Type</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Store</t>
+  </si>
+  <si>
+    <t>Original Price</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>Date Received</t>
+  </si>
+  <si>
+    <t>Date Ended</t>
+  </si>
+  <si>
+    <t>Bipro Classic Megaplex Cookies and Cream</t>
+  </si>
+  <si>
+    <t>Bipro Classic Megaplex Chocolate</t>
+  </si>
+  <si>
+    <t>Fees</t>
+  </si>
+  <si>
+    <t>Creatine</t>
+  </si>
+  <si>
+    <t>Amount (lb or g)</t>
+  </si>
+  <si>
+    <t>Optimum Nutrition 5g</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Creatina Monohidratada Atomic 120 Servicios</t>
+  </si>
+  <si>
+    <t>Bipro Classic Megaplex Capuccino &amp; Whiskey Cream</t>
+  </si>
+  <si>
+    <t>External</t>
+  </si>
+  <si>
+    <t>Rappi - Zona Fit</t>
+  </si>
+  <si>
+    <t>Bipro Mass Vainilla</t>
+  </si>
+  <si>
+    <t>Rappi - Nutramerican</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0\ [$COP]"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -271,7 +333,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -293,6 +355,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,113 +488,167 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="41">
+  <dxfs count="53">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="#,##0\ [$COP]"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="#,##0\ [$COP]"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="#,##0\ [$COP]"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -552,19 +674,52 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -585,16 +740,33 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -615,196 +787,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
@@ -877,13 +859,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -899,20 +874,13 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -981,13 +949,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1003,6 +964,124 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <top style="thin">
           <color indexed="64"/>
@@ -1010,6 +1089,31 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="thin">
           <color indexed="64"/>
@@ -1017,23 +1121,41 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1049,24 +1171,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{15674E66-94AB-4C3C-93BE-CEC40F8CE96A}" name="Tabla2" displayName="Tabla2" ref="E2:F5" totalsRowShown="0" headerRowDxfId="5" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{15674E66-94AB-4C3C-93BE-CEC40F8CE96A}" name="Tabla2" displayName="Tabla2" ref="E2:F5" totalsRowShown="0" headerRowDxfId="52" dataDxfId="51">
   <autoFilter ref="E2:F5" xr:uid="{15674E66-94AB-4C3C-93BE-CEC40F8CE96A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{95C25A2A-BBED-4D1D-AC5F-20A4A79B2005}" name="Macronutrient" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{9A5BF5C9-E432-40E7-8FF9-E46462FB5688}" name="Calories per gram [kcal/g]" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{95C25A2A-BBED-4D1D-AC5F-20A4A79B2005}" name="Macronutrient" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{9A5BF5C9-E432-40E7-8FF9-E46462FB5688}" name="Calories per gram [kcal/g]" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6DE86699-F353-4B85-BFA7-87A0C8711DEC}" name="Tabla3" displayName="Tabla3" ref="E7:H11" totalsRowShown="0" headerRowDxfId="18" dataDxfId="19" headerRowBorderDxfId="38" tableBorderDxfId="39" totalsRowBorderDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6DE86699-F353-4B85-BFA7-87A0C8711DEC}" name="Tabla3" displayName="Tabla3" ref="E7:H11" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" totalsRowBorderDxfId="44">
   <autoFilter ref="E7:H11" xr:uid="{6DE86699-F353-4B85-BFA7-87A0C8711DEC}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{1340CE2A-0150-4AFA-8743-34A22C06FB6D}" name="Macronutrient" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{27DFE90D-8D4C-425E-A781-5583C11EF34D}" name="Grams [g/day]" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{B575E2A2-46F8-436A-A50E-D3EB261BDD4B}" name="Calories [kcal/day]" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{CD804383-57E5-434A-9136-5528A3D56614}" name="Percentage [%]" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{1340CE2A-0150-4AFA-8743-34A22C06FB6D}" name="Macronutrient" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{27DFE90D-8D4C-425E-A781-5583C11EF34D}" name="Grams [g/day]" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{B575E2A2-46F8-436A-A50E-D3EB261BDD4B}" name="Calories [kcal/day]" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{CD804383-57E5-434A-9136-5528A3D56614}" name="Percentage [%]" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1077,14 +1199,14 @@
   <autoFilter ref="B18:C21" xr:uid="{C56B39AD-346B-4EE4-B7F6-47DA415118EC}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{8953FD21-EF3D-4C48-8247-F1E58B13A854}" name="Planning"/>
-    <tableColumn id="2" xr3:uid="{4C7CC28D-E53E-4814-86BE-356B88CDFAC4}" name="Duration [week]" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{4C7CC28D-E53E-4814-86BE-356B88CDFAC4}" name="Duration [week]" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A1E3A1E5-51DB-4063-8F01-74AAD76E806D}" name="Table6" displayName="Table6" ref="B9:C11" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30" headerRowBorderDxfId="35" tableBorderDxfId="36" totalsRowBorderDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A1E3A1E5-51DB-4063-8F01-74AAD76E806D}" name="Table6" displayName="Table6" ref="B9:C11" totalsRowShown="0" headerRowDxfId="38" dataDxfId="36" headerRowBorderDxfId="37" tableBorderDxfId="35" totalsRowBorderDxfId="34">
   <autoFilter ref="B9:C11" xr:uid="{A1E3A1E5-51DB-4063-8F01-74AAD76E806D}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{5D747E8C-AE4A-4668-AFD5-B53374E0D898}" name="Supplements" dataDxfId="33"/>
@@ -1095,40 +1217,63 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C3B0FD24-7FBE-4A08-B9B6-1384D67FC4F5}" name="Table7" displayName="Table7" ref="B2:C7" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="28" tableBorderDxfId="29" totalsRowBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C3B0FD24-7FBE-4A08-B9B6-1384D67FC4F5}" name="Table7" displayName="Table7" ref="B2:C7" totalsRowShown="0" headerRowDxfId="31" headerRowBorderDxfId="30" tableBorderDxfId="29" totalsRowBorderDxfId="28">
   <autoFilter ref="B2:C7" xr:uid="{C3B0FD24-7FBE-4A08-B9B6-1384D67FC4F5}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D1B1051C-715F-4B3B-9807-BAD623C403BD}" name="Objective" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{83B368C2-F2E8-43AD-9B7D-A75FA78ED617}" name="Lean Bulk" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{D1B1051C-715F-4B3B-9807-BAD623C403BD}" name="Objective" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{83B368C2-F2E8-43AD-9B7D-A75FA78ED617}" name="Lean Bulk" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CF92E4DD-0CEA-45D6-8117-157DA519EF2D}" name="Tabla4" displayName="Tabla4" ref="B2:E9" totalsRowShown="0" headerRowDxfId="11" dataDxfId="12" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CF92E4DD-0CEA-45D6-8117-157DA519EF2D}" name="Tabla4" displayName="Tabla4" ref="B2:E9" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="21">
   <autoFilter ref="B2:E9" xr:uid="{CF92E4DD-0CEA-45D6-8117-157DA519EF2D}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{35519578-9760-48C4-A75A-7F84FBB87DF1}" name="Meal" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{9FFC3B3C-22A1-4FA9-867C-6FA56933045B}" name="Time" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{FC36E678-1895-415B-B48B-18F8978EBEDB}" name="Calories [kcal]" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{56363AD3-E144-4C8E-89EA-820ADCCAE317}" name="Meals" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{35519578-9760-48C4-A75A-7F84FBB87DF1}" name="Meal" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{9FFC3B3C-22A1-4FA9-867C-6FA56933045B}" name="Time" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{FC36E678-1895-415B-B48B-18F8978EBEDB}" name="Calories [kcal]" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{56363AD3-E144-4C8E-89EA-820ADCCAE317}" name="Meals" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{065700C1-DA18-4652-854E-DCD299B5431C}" name="Tabla1" displayName="Tabla1" ref="B2:F9" totalsRowShown="0" headerRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{065700C1-DA18-4652-854E-DCD299B5431C}" name="Tabla1" displayName="Tabla1" ref="B2:F9" totalsRowShown="0" headerRowDxfId="16">
   <autoFilter ref="B2:F9" xr:uid="{065700C1-DA18-4652-854E-DCD299B5431C}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{83833A54-B244-4087-8347-A1F2344F32E8}" name="Parameter"/>
-    <tableColumn id="2" xr3:uid="{34BFC17B-89EA-4A89-A76C-8B52AD4867E1}" name="IDEAL" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{5B9AF230-9800-4346-9888-4BC0AA5E52E6}" name="12.10.2024" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{5067B4CE-50FE-4C15-A13A-42E363C05A76}" name="30.05.2025" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{C068203D-3C5E-40C6-BFFF-0F40843423D6}" name="12.06.2025" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{34BFC17B-89EA-4A89-A76C-8B52AD4867E1}" name="IDEAL" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{5B9AF230-9800-4346-9888-4BC0AA5E52E6}" name="12.10.2024" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{5067B4CE-50FE-4C15-A13A-42E363C05A76}" name="30.05.2025" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{C068203D-3C5E-40C6-BFFF-0F40843423D6}" name="12.06.2025" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{5E3B3B0D-6845-4169-B0BA-2292A30A5F40}" name="Table8" displayName="Table8" ref="C2:L8" totalsRowShown="0" headerRowDxfId="11" dataDxfId="2">
+  <autoFilter ref="C2:L8" xr:uid="{5E3B3B0D-6845-4169-B0BA-2292A30A5F40}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{3B411F57-453F-4051-9E39-F60F730D2C72}" name="Supplement Type" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{204D2256-F3A9-4D32-AB9F-95C1934BAAC3}" name="Reference" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{A2D20382-A434-417D-ACC3-83C799594F4D}" name="Amount (lb or g)" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{586F240C-6F00-4AD6-A9EF-1B5C7017719D}" name="Store" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{28A5B6E4-94EE-49E5-BB00-35BF16A117A3}" name="Original Price" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{F3B6777B-D0BA-4156-A8B4-3D181512C7E2}" name="Total Cost" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{D2681CCD-FB40-4F16-B349-652A89080AEB}" name="Fees" dataDxfId="4">
+      <calculatedColumnFormula>Table8[[#This Row],[Total Cost]]-Table8[[#This Row],[Original Price]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{5F404EA7-BAC8-4ADC-B986-C24D611232A4}" name="Date Received" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{B3A9E8ED-4C6A-443B-9388-A9B90D4BA98F}" name="Date Ended" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{BAC68445-82C6-45C5-8246-0A66759100AA}" name="Duration" dataDxfId="0">
+      <calculatedColumnFormula>(Table8[[#This Row],[Date Ended]] - Table8[[#This Row],[Date Received]])/30</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1446,183 +1591,183 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="32" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="6">
         <v>25</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="30">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <v>175</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="30">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="10">
         <f>10*'Measures Tracker'!F3+6.25*C4-5*C3+5</f>
         <v>1617.75</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="30">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="10">
         <f>C5*1.725</f>
         <v>2790.6187500000001</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="11">
         <f>C6*1.15</f>
         <v>3209.2115624999997</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="17" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="9">
         <f>'Measures Tracker'!F3*2.3</f>
         <v>148.12</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="9">
         <f>F8*F3</f>
         <v>592.48</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="10">
         <f>G8*100/$C$7</f>
         <v>18.461855457682997</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="9">
         <f>(C7-(F8*4+F10*9))/4</f>
         <v>509.28289062499994</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="9">
         <f>F9*F4</f>
         <v>2037.1315624999997</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="10">
         <f>G9*100/$C$7</f>
         <v>63.47763376849668</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="6">
         <v>5</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="9">
         <f>'Measures Tracker'!F3*1</f>
         <v>64.400000000000006</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="9">
         <f>F10*F5</f>
         <v>579.6</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="10">
         <f>G10*100/$C$7</f>
         <v>18.060510773820322</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="8">
         <v>20</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="14">
         <f>SUM(F8:F10)</f>
         <v>721.80289062499992</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="14">
         <f>SUM(G8:G10)</f>
         <v>3209.2115624999997</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="15">
         <f>SUM(H8:H10)</f>
         <v>100</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="36"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
@@ -1691,114 +1836,114 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="26" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="3" spans="2:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="18">
         <v>0.19791666666666666</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="20" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="4" spans="2:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="18">
         <v>0.36458333333333331</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="20" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="18">
         <v>0.47916666666666669</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="20" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="18">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="18">
         <v>0.70833333333333337</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="18">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="19">
         <v>700</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="21">
         <v>0.89583333333333337</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="23" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1821,19 +1966,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="34" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1841,16 +1986,16 @@
       <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="31">
+      <c r="C3" s="29">
         <v>66</v>
       </c>
-      <c r="D3" s="32">
+      <c r="D3" s="30">
         <v>65.5</v>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="30">
         <v>63.9</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="30">
         <v>64.400000000000006</v>
       </c>
     </row>
@@ -1858,16 +2003,16 @@
       <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="29">
         <v>12</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="30">
         <v>15</v>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="30">
         <v>14.3</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="30">
         <v>14.1</v>
       </c>
     </row>
@@ -1875,16 +2020,16 @@
       <c r="B5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="30">
         <v>57.55</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="30">
         <v>59.3</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="30">
         <v>57.92</v>
       </c>
     </row>
@@ -1892,16 +2037,16 @@
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="30">
         <v>52.9</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="30">
         <v>52</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="30">
         <v>52.4</v>
       </c>
     </row>
@@ -1909,16 +2054,16 @@
       <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="30">
         <v>2.76</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="30">
         <v>2.8</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="30">
         <v>2.79</v>
       </c>
     </row>
@@ -1926,16 +2071,16 @@
       <c r="B8" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="29">
         <v>1</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="30">
         <v>2</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="30">
         <v>2</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="31">
         <v>2</v>
       </c>
     </row>
@@ -1943,17 +2088,278 @@
       <c r="B9" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="29">
         <v>12</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="30">
         <v>15</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="30">
         <v>15</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="30">
         <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6149BCD-10A2-401C-9949-3E92484370A8}">
+  <dimension ref="C2:P8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="47.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C2" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C3" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="30">
+        <v>3</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3" s="38">
+        <v>202490</v>
+      </c>
+      <c r="H3" s="38">
+        <v>229890</v>
+      </c>
+      <c r="I3" s="38">
+        <f>Table8[[#This Row],[Total Cost]]-Table8[[#This Row],[Original Price]]</f>
+        <v>27400</v>
+      </c>
+      <c r="J3" s="39">
+        <v>45968</v>
+      </c>
+      <c r="K3" s="39">
+        <v>46093</v>
+      </c>
+      <c r="L3" s="40">
+        <f>(Table8[[#This Row],[Date Ended]] - Table8[[#This Row],[Date Received]])/30</f>
+        <v>4.166666666666667</v>
+      </c>
+    </row>
+    <row r="4" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C4" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="30">
+        <v>2</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="38">
+        <v>175490</v>
+      </c>
+      <c r="H4" s="38">
+        <v>204990</v>
+      </c>
+      <c r="I4" s="38">
+        <f>Table8[[#This Row],[Total Cost]]-Table8[[#This Row],[Original Price]]</f>
+        <v>29500</v>
+      </c>
+      <c r="J4" s="39">
+        <v>46093</v>
+      </c>
+      <c r="K4" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="40" t="e">
+        <f>(Table8[[#This Row],[Date Ended]] - Table8[[#This Row],[Date Received]])/30</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="5" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C5" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="30">
+        <v>3</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="38">
+        <v>265000</v>
+      </c>
+      <c r="H5" s="38">
+        <v>265000</v>
+      </c>
+      <c r="I5" s="38">
+        <f>Table8[[#This Row],[Total Cost]]-Table8[[#This Row],[Original Price]]</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="39">
+        <v>46174</v>
+      </c>
+      <c r="K5" s="39">
+        <v>46304</v>
+      </c>
+      <c r="L5" s="40">
+        <f>(Table8[[#This Row],[Date Ended]] - Table8[[#This Row],[Date Received]])/30</f>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="P5" s="37"/>
+    </row>
+    <row r="6" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C6" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="30">
+        <v>300</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="38">
+        <v>170000</v>
+      </c>
+      <c r="H6" s="38">
+        <v>170000</v>
+      </c>
+      <c r="I6" s="38">
+        <f>Table8[[#This Row],[Total Cost]]-Table8[[#This Row],[Original Price]]</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" s="40" t="e">
+        <f>(Table8[[#This Row],[Date Ended]] - Table8[[#This Row],[Date Received]])/30</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C7" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="30">
+        <v>600</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="38">
+        <v>115000</v>
+      </c>
+      <c r="H7" s="38">
+        <v>132000</v>
+      </c>
+      <c r="I7" s="38">
+        <f>Table8[[#This Row],[Total Cost]]-Table8[[#This Row],[Original Price]]</f>
+        <v>17000</v>
+      </c>
+      <c r="J7" s="39">
+        <v>46174</v>
+      </c>
+      <c r="K7" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="40" t="e">
+        <f>(Table8[[#This Row],[Date Ended]] - Table8[[#This Row],[Date Received]])/30</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C8" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="30">
+        <v>3</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="38">
+        <v>224100</v>
+      </c>
+      <c r="H8" s="38">
+        <v>246000</v>
+      </c>
+      <c r="I8" s="38">
+        <f>Table8[[#This Row],[Total Cost]]-Table8[[#This Row],[Original Price]]</f>
+        <v>21900</v>
+      </c>
+      <c r="J8" s="39">
+        <v>46304</v>
+      </c>
+      <c r="K8" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="40" t="e">
+        <f>(Table8[[#This Row],[Date Ended]] - Table8[[#This Row],[Date Received]])/30</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
